--- a/data/LCIs/Roy_2025/Ni_LCIs_BW_from_S1.xlsx
+++ b/data/LCIs/Roy_2025/Ni_LCIs_BW_from_S1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/fasc_metal_sustainability/data/LCIs/Roy_2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="273" documentId="11_E811C2F32C30F0A3B7709A196033EA5355473EBC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6606FDEB-9281-40F8-BBAD-64B886412C20}"/>
+  <xr:revisionPtr revIDLastSave="305" documentId="11_E811C2F32C30F0A3B7709A196033EA5355473EBC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01C62C64-F2A9-4577-8085-17299E5A15ED}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="8925" yWindow="3375" windowWidth="21600" windowHeight="11175" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Note" sheetId="8" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="111">
   <si>
     <t>database</t>
   </si>
@@ -118,9 +118,6 @@
     <t>sulfuric acid</t>
   </si>
   <si>
-    <t>Carbon dioxide</t>
-  </si>
-  <si>
     <t>electricity, high voltage, production mix</t>
   </si>
   <si>
@@ -133,9 +130,6 @@
     <t>ammonia, anhydrous, liquid</t>
   </si>
   <si>
-    <t>air separation, cryogenic</t>
-  </si>
-  <si>
     <t>oxygen, liquid</t>
   </si>
   <si>
@@ -193,9 +187,6 @@
     <t>heat production, at hard coal industrial furnace 1-10MW</t>
   </si>
   <si>
-    <t>ON</t>
-  </si>
-  <si>
     <t>market for silica sand</t>
   </si>
   <si>
@@ -205,12 +196,6 @@
     <t>heat production, at coal coke industrial furnace 1-10MW</t>
   </si>
   <si>
-    <t>market for hydrogen, liquid</t>
-  </si>
-  <si>
-    <t>hydrogen, liquid</t>
-  </si>
-  <si>
     <t>Source</t>
   </si>
   <si>
@@ -262,9 +247,6 @@
     <t>technosphere</t>
   </si>
   <si>
-    <t>Flash smelting of sulfide ores</t>
-  </si>
-  <si>
     <t>nickel mine operation and benefication to nickel concentrate, 16% Ni</t>
   </si>
   <si>
@@ -274,9 +256,6 @@
     <t>ecoinvent 3.10 cutoff</t>
   </si>
   <si>
-    <t>Ni Sofia Roy</t>
-  </si>
-  <si>
     <t>skip</t>
   </si>
   <si>
@@ -370,10 +349,25 @@
     <t>Sulfuric acid</t>
   </si>
   <si>
-    <t>Water, unspecified origin</t>
-  </si>
-  <si>
     <t>Pyrometallurical sulfide ore</t>
+  </si>
+  <si>
+    <t>Nickel Sofia Roy</t>
+  </si>
+  <si>
+    <t>Carbon dioxide, fossil</t>
+  </si>
+  <si>
+    <t>Water, unspecified natural origin</t>
+  </si>
+  <si>
+    <t>market for hydrogen, gaseous, low pressure</t>
+  </si>
+  <si>
+    <t>hydrogen, gaseous, low pressure</t>
+  </si>
+  <si>
+    <t>industrial gases production, cryogenic air separation</t>
   </si>
 </sst>
 </file>
@@ -408,12 +402,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -428,7 +428,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -440,6 +440,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -462,15 +463,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>258232</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>58328</xdr:rowOff>
+      <xdr:colOff>477307</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>172628</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -493,7 +494,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12477750" y="0"/>
+          <a:off x="12696825" y="495300"/>
           <a:ext cx="7573432" cy="8440328"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -884,7 +885,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="55" customWidth="1"/>
@@ -892,23 +893,31 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -918,7 +927,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="55" customWidth="1"/>
@@ -929,544 +938,552 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>1</v>
+      <c r="A1" t="s">
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s">
-        <v>41</v>
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>71</v>
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B9" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D11" s="1">
         <v>1</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>76</v>
-      </c>
-      <c r="B10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10" t="s">
-        <v>49</v>
-      </c>
-      <c r="D10">
-        <v>7.79</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>78</v>
-      </c>
-      <c r="G10" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>42</v>
-      </c>
-      <c r="B11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11">
-        <v>3.64</v>
-      </c>
-      <c r="E11" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" t="s">
-        <v>78</v>
-      </c>
-      <c r="G11" t="s">
-        <v>74</v>
-      </c>
+      <c r="E11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D12">
-        <v>2.2799999999999998</v>
+        <v>7.79</v>
       </c>
       <c r="E12" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G12" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="D13">
-        <v>3.06</v>
+        <v>3.64</v>
       </c>
       <c r="E13" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F13" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G13" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="D14">
-        <v>3.54</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="E14" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="F14" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G14" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D15">
-        <v>8.1999999999999993</v>
+        <v>3.06</v>
       </c>
       <c r="E15" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F15" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G15" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="D16">
-        <v>6.24</v>
+        <v>3.54</v>
       </c>
       <c r="E16" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="F16" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G16" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B17" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D17">
-        <v>11.22</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="E17" t="s">
         <v>15</v>
       </c>
       <c r="F17" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G17" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C18" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D18">
-        <v>0.49</v>
+        <v>6.24</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F18" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G18" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B19" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="C19" t="s">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="D19">
-        <v>2.2400000000000002</v>
+        <v>11.22</v>
       </c>
       <c r="E19" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F19" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G19" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>55</v>
-      </c>
-      <c r="B20" t="s">
-        <v>29</v>
+      <c r="A20" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="C20" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D20">
-        <v>9.01</v>
+        <v>0.49</v>
       </c>
       <c r="E20" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G20" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="B21" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="C21" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="D21">
-        <v>0.7</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="E21" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G21" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B22" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="C22" t="s">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="D22">
-        <v>0.28999999999999998</v>
+        <v>9.01</v>
       </c>
       <c r="E22" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F22" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G22" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="B23" t="s">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="C23" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="D23">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="E23" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="F23" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G23" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="C24" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D24">
-        <v>0.64</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G24" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="B25" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="C25" t="s">
         <v>17</v>
       </c>
       <c r="D25">
-        <v>7.0000000000000007E-2</v>
+        <v>0.91</v>
       </c>
       <c r="E25" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="F25" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G25" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" t="s">
+        <v>17</v>
+      </c>
+      <c r="D26">
+        <v>0.64</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" t="s">
+        <v>72</v>
+      </c>
+      <c r="G26" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C27" t="s">
+        <v>17</v>
+      </c>
+      <c r="D27">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" t="s">
+        <v>72</v>
+      </c>
+      <c r="G27" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
         <v>16</v>
       </c>
-      <c r="C26" t="s">
-        <v>45</v>
-      </c>
-      <c r="D26">
+      <c r="C28" t="s">
+        <v>43</v>
+      </c>
+      <c r="D28">
         <v>2.9</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E28" t="s">
         <v>18</v>
       </c>
-      <c r="F26" t="s">
-        <v>78</v>
-      </c>
-      <c r="G26" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>48</v>
-      </c>
-      <c r="B27" t="s">
+      <c r="F28" t="s">
+        <v>72</v>
+      </c>
+      <c r="G28" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>46</v>
+      </c>
+      <c r="B29" t="s">
         <v>22</v>
       </c>
-      <c r="C27" t="s">
-        <v>49</v>
-      </c>
-      <c r="D27">
+      <c r="C29" t="s">
+        <v>47</v>
+      </c>
+      <c r="D29">
         <v>18.5</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E29" t="s">
         <v>15</v>
       </c>
-      <c r="F27" t="s">
-        <v>78</v>
-      </c>
-      <c r="G27" t="s">
-        <v>74</v>
+      <c r="F29" t="s">
+        <v>72</v>
+      </c>
+      <c r="G29" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1491,7 +1508,7 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -1507,7 +1524,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -1531,7 +1548,7 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -1559,39 +1576,39 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="L8" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="M8" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="N8" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1600,21 +1617,21 @@
         <v>8</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="G9" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D10">
         <v>4.79</v>
@@ -1623,18 +1640,18 @@
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G10" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
         <v>5</v>
@@ -1647,18 +1664,18 @@
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G11" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B12" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
@@ -1671,18 +1688,18 @@
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G12" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
         <v>5</v>
@@ -1695,18 +1712,18 @@
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G13" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -1719,18 +1736,18 @@
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G14" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -1743,18 +1760,18 @@
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G15" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -1767,18 +1784,18 @@
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G16" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
         <v>5</v>
@@ -1790,21 +1807,21 @@
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G17" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B18" t="s">
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D18">
         <v>11.43</v>
@@ -1813,21 +1830,21 @@
         <v>18</v>
       </c>
       <c r="F18" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G18" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C19" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D19">
         <v>0.02</v>
@@ -1836,21 +1853,21 @@
         <v>15</v>
       </c>
       <c r="F19" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G19" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D20">
         <v>0.32</v>
@@ -1859,18 +1876,18 @@
         <v>15</v>
       </c>
       <c r="F20" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G20" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B21" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C21" t="s">
         <v>17</v>
@@ -1882,18 +1899,18 @@
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G21" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="B22" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C22" t="s">
         <v>17</v>
@@ -1906,10 +1923,10 @@
         <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G22" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1929,18 +1946,18 @@
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G23" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C24" t="s">
         <v>17</v>
@@ -1952,18 +1969,18 @@
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G24" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="B25" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C25" t="s">
         <v>5</v>
@@ -1975,18 +1992,18 @@
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G25" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C26" t="s">
         <v>5</v>
@@ -1998,18 +2015,18 @@
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G26" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C27" t="s">
         <v>5</v>
@@ -2021,18 +2038,18 @@
         <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G27" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="B28" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C28" t="s">
         <v>5</v>
@@ -2044,18 +2061,18 @@
         <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G28" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B29" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C29" t="s">
         <v>5</v>
@@ -2067,10 +2084,10 @@
         <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G29" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -2081,7 +2098,7 @@
         <v>24</v>
       </c>
       <c r="C30" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D30">
         <v>0.01</v>
@@ -2090,10 +2107,10 @@
         <v>8</v>
       </c>
       <c r="F30" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G30" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -2113,15 +2130,15 @@
         <v>8</v>
       </c>
       <c r="F31" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G31" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>27</v>
+        <v>106</v>
       </c>
       <c r="D32">
         <f>0.0015</f>
@@ -2131,18 +2148,18 @@
         <v>8</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D33">
         <f>0.0000007</f>
@@ -2152,18 +2169,18 @@
         <v>8</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="D34">
         <f>0.00001</f>
@@ -2173,18 +2190,18 @@
         <v>8</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D35">
         <f>0.00003</f>
@@ -2194,18 +2211,18 @@
         <v>8</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D36">
         <f>0.00027</f>
@@ -2215,18 +2232,18 @@
         <v>8</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="D37">
         <f>0.00008</f>
@@ -2236,18 +2253,18 @@
         <v>8</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="D38">
         <f>0.00000125</f>
@@ -2257,18 +2274,18 @@
         <v>8</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D39">
         <f>0.00000356</f>
@@ -2278,18 +2295,18 @@
         <v>8</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D40">
         <f>0.00018</f>
@@ -2299,18 +2316,18 @@
         <v>8</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="D41">
         <f>0.00167</f>
@@ -2320,18 +2337,18 @@
         <v>8</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="D42">
         <f>0.00171</f>
@@ -2341,18 +2358,18 @@
         <v>8</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="D43">
         <f>0.00377</f>
@@ -2362,18 +2379,18 @@
         <v>8</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="D44">
         <f>0.00013</f>
@@ -2383,18 +2400,18 @@
         <v>8</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D45">
         <v>0.08</v>
@@ -2403,13 +2420,13 @@
         <v>21</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
